--- a/web/models/NonLIHTC_engine_template.xlsx
+++ b/web/models/NonLIHTC_engine_template.xlsx
@@ -13317,7 +13317,7 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="B2:L42"/>
+  <dimension ref="B2:L45"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25" customWidth="1"/>
@@ -14286,6 +14286,36 @@
       <c r="K42" s="248"/>
       <c r="L42" s="249"/>
     </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C43" s="248" t="inlineStr">
+        <is>
+          <t>Subordinate / Soft Debt — Amount</t>
+        </is>
+      </c>
+      <c r="D43" s="338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C44" s="248" t="inlineStr">
+        <is>
+          <t>Sub Rate</t>
+        </is>
+      </c>
+      <c r="D44" s="338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C45" s="248" t="inlineStr">
+        <is>
+          <t>Sub Amort (yrs; 0 = IO/deferred)</t>
+        </is>
+      </c>
+      <c r="D45" s="338">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C3:K3"/>
@@ -14302,7 +14332,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B2:U45"/>
+  <dimension ref="B2:U49"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="32" customWidth="1"/>
@@ -15397,56 +15427,56 @@
         <v>438</v>
       </c>
       <c r="D20" s="358">
-        <f>IFERROR(SUMPRODUCT(D7:D19,E7:E19),0)</f>
+        <f>IFERROR(SUMPRODUCT(D7:D19,E7:E19)+SUMPRODUCT(D46:D49,E46:E49),0)</f>
         <v>0</v>
       </c>
       <c r="E20" s="358">
-        <f>IFERROR(SUM(E7:E19),0)</f>
-        <v>224</v>
+        <f>IFERROR(SUM(E7:E19,E46:E49),0)</f>
+        <v>0</v>
       </c>
       <c r="F20" s="359">
-        <f>IFERROR(SUMPRODUCT(E7:E19,F7:F19)/E20,0)</f>
+        <f>IFERROR((SUMPRODUCT(E7:E19,F7:F19)+SUMPRODUCT(E46:E49,F46:F49))/E20,0)</f>
         <v>0</v>
       </c>
       <c r="G20" s="359">
-        <f>IFERROR(SUMPRODUCT(E7:E19,G7:G19)/E20,0)</f>
-        <v>10.21875</v>
+        <f>IFERROR((SUMPRODUCT(E7:E19,G7:G19)+SUMPRODUCT(E46:E49,G46:G49))/E20,0)</f>
+        <v>0</v>
       </c>
       <c r="H20" s="359">
-        <f>IFERROR(SUM(H7:H19),0)</f>
-        <v>2289</v>
+        <f>IFERROR(SUM(H7:H19,H46:H49),0)</f>
+        <v>0</v>
       </c>
       <c r="I20" s="359">
-        <f>IFERROR(SUMPRODUCT($E$7:$E$19,I7:I19)/Inputs!H14,0)</f>
-        <v>2289</v>
+        <f>IFERROR((SUMPRODUCT($E$7:$E$19,I7:I19)+SUMPRODUCT($E$46:$E$49,I46:I49))/Inputs!H14,0)</f>
+        <v>0</v>
       </c>
       <c r="J20" s="360">
-        <f>IFERROR(SUMPRODUCT(E7:E19,J7:J19)/E20,0)</f>
-        <v>1</v>
+        <f>IFERROR((SUMPRODUCT(E7:E19,J7:J19)+SUMPRODUCT(E46:E49,J46:J49))/E20,0)</f>
+        <v>0</v>
       </c>
       <c r="K20" s="359">
-        <f>IFERROR(SUMPRODUCT($E$7:$E$19,K7:K19)/Inputs!H14,0)</f>
-        <v>2289</v>
+        <f>IFERROR((SUMPRODUCT($E$7:$E$19,K7:K19)+SUMPRODUCT($E$46:$E$49,K46:K49))/Inputs!H14,0)</f>
+        <v>0</v>
       </c>
       <c r="L20" s="359">
         <f t="shared" si="4"/>
         <v>512736</v>
       </c>
       <c r="M20" s="360">
-        <f>IFERROR(SUMPRODUCT(M7:M19,$L$7:$L$19)/$L$20,0)</f>
-        <v>2.5000000000000001E-2</v>
+        <f>IFERROR((SUMPRODUCT(M7:M19,$L$7:$L$19)+SUMPRODUCT(M46:M49,L46:L49))/$L$20,0)</f>
+        <v>0</v>
       </c>
       <c r="N20" s="360">
-        <f>IFERROR(SUMPRODUCT(N7:N19,$L$7:$L$19)/$L$20,0)</f>
-        <v>0.03</v>
+        <f>IFERROR((SUMPRODUCT(N7:N19,$L$7:$L$19)+SUMPRODUCT(N46:N49,L46:L49))/$L$20,0)</f>
+        <v>0</v>
       </c>
       <c r="O20" s="358">
         <f>IFERROR(P20/E20,0)</f>
         <v>419</v>
       </c>
       <c r="P20" s="358">
-        <f>IFERROR(SUM(P7:P19),0)</f>
-        <v>93856</v>
+        <f>IFERROR(SUM(P7:P19,P46:P49),0)</f>
+        <v>0</v>
       </c>
       <c r="Q20" s="358">
         <f>IFERROR(L20/P20,0)</f>
@@ -15457,8 +15487,8 @@
         <v>100</v>
       </c>
       <c r="S20" s="358">
-        <f>IFERROR(SUM(S7:S19),0)</f>
-        <v>22400</v>
+        <f>IFERROR(SUM(S7:S19,S46:S49),0)</f>
+        <v>0</v>
       </c>
       <c r="T20" s="191"/>
       <c r="U20" s="190"/>
@@ -15604,7 +15634,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="229">
-        <f>IFERROR(+E8+E12+E16,0)</f>
+        <f>IFERROR(+E8+E12+E16+E46,0)</f>
         <v>0</v>
       </c>
       <c r="O24" s="251">
@@ -15652,8 +15682,8 @@
         <v>1</v>
       </c>
       <c r="N25" s="211">
-        <f>IFERROR(+E9+E13+E17+E7,0)</f>
-        <v>224</v>
+        <f>IFERROR(+E9+E13+E17+E7+E47,0)</f>
+        <v>0</v>
       </c>
       <c r="O25" s="270">
         <f>+IFERROR((P7+P9+P13+P17)/N25,0)</f>
@@ -15712,7 +15742,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="229">
-        <f>IFERROR(+E10+E14+E18,0)</f>
+        <f>IFERROR(+E10+E14+E18+E48,0)</f>
         <v>0</v>
       </c>
       <c r="O26" s="251">
@@ -15776,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="211">
-        <f>IFERROR(+E11+E15+E19,0)</f>
+        <f>IFERROR(+E11+E15+E19+E49,0)</f>
         <v>0</v>
       </c>
       <c r="O27" s="270">
@@ -15857,16 +15887,16 @@
         <v>0</v>
       </c>
       <c r="R28" s="369">
-        <f>IFERROR(+SUM(H12:H19)/SUM(E12:E19),0)</f>
+        <f>IFERROR(+SUM(H12:H19,H46:H49)/SUM(E12:E19,E46:E49),0)</f>
         <v>0</v>
       </c>
       <c r="S28" s="369">
-        <f>IFERROR(+SUM(L12:L19)/SUM(E12:E19),0)</f>
-        <v>2289</v>
+        <f>IFERROR(+SUM(L12:L19,L46:L49)/SUM(E12:E19,E46:E49),0)</f>
+        <v>0</v>
       </c>
       <c r="T28" s="370">
-        <f>IFERROR(+SUM(L12:L19)/(SUM(P12:P19)),0)</f>
-        <v>5.4630071599045342</v>
+        <f>IFERROR(+SUM(L12:L19,L46:L49)/(SUM(P12:P19,P46:P49)),0)</f>
+        <v>0</v>
       </c>
       <c r="U28" s="190"/>
     </row>
@@ -16310,12 +16340,12 @@
         <v>0</v>
       </c>
       <c r="R36" s="369">
-        <f>IFERROR(+SUM(H12:H19)/SUM(E12:E19)*Inputs!$F$34,0)</f>
+        <f>IFERROR(+SUM(H12:H19,H46:H49)/SUM(E12:E19,E46:E49)*Inputs!$F$34,0)</f>
         <v>0</v>
       </c>
       <c r="S36" s="369">
-        <f>IFERROR(+SUM(L12:L19)/SUM(E12:E19)*Inputs!$F$34,0)</f>
-        <v>2444.7967921507388</v>
+        <f>IFERROR(+SUM(L12:L19,L46:L49)/SUM(E12:E19,E46:E49)*Inputs!$F$34,0)</f>
+        <v>0</v>
       </c>
       <c r="T36" s="370">
         <f>+IFERROR(S36/O36,0)</f>
@@ -16620,6 +16650,302 @@
       <c r="T45" s="11"/>
       <c r="U45" s="11"/>
     </row>
+    <row r="46" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="189"/>
+      <c r="C46" s="354" t="inlineStr">
+        <is>
+          <t>Restricted Tier C 0BR</t>
+        </is>
+      </c>
+      <c r="D46" s="340">
+        <f>IFERROR(1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E46" s="340">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="342">
+        <f>IFERROR(G46*E46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="343">
+        <f>IFERROR(100/100,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K46" s="342">
+        <f>IFERROR((I46-G46)*J46+G46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="342">
+        <f>IFERROR(K46*E46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="343">
+        <f>IFERROR(+Inputs!$L$7,0)</f>
+        <v>2.5E-2</v>
+      </c>
+      <c r="N46" s="343">
+        <f>IFERROR(+Inputs!$L$6,0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="O46" s="340">
+        <f>IFERROR(O8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P46" s="340">
+        <f>IFERROR(O46*E46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="342">
+        <f>IFERROR(K46/O46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R46" s="340">
+        <f>IFERROR(100,0)</f>
+        <v>100</v>
+      </c>
+      <c r="S46" s="340">
+        <f>IFERROR(R46*E46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T46" s="191"/>
+      <c r="U46" s="190"/>
+    </row>
+    <row r="47" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="189"/>
+      <c r="C47" s="354" t="inlineStr">
+        <is>
+          <t>Restricted Tier C 1BR</t>
+        </is>
+      </c>
+      <c r="D47" s="340">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="340">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="342">
+        <f>IFERROR(G47*E47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="343">
+        <f>IFERROR(100/100,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K47" s="342">
+        <f>IFERROR((I47-G47)*J47+G47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="342">
+        <f>IFERROR(K47*E47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="343">
+        <f>IFERROR(+Inputs!$L$7,0)</f>
+        <v>2.5E-2</v>
+      </c>
+      <c r="N47" s="343">
+        <f>IFERROR(+Inputs!$L$6,0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="O47" s="340">
+        <f>IFERROR(O9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P47" s="340">
+        <f>IFERROR(O47*E47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q47" s="342">
+        <f>IFERROR(K47/O47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R47" s="340">
+        <f>IFERROR(100,0)</f>
+        <v>100</v>
+      </c>
+      <c r="S47" s="340">
+        <f>IFERROR(R47*E47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T47" s="191"/>
+      <c r="U47" s="190"/>
+    </row>
+    <row r="48" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="189"/>
+      <c r="C48" s="354" t="inlineStr">
+        <is>
+          <t>Restricted Tier C 2BR</t>
+        </is>
+      </c>
+      <c r="D48" s="340">
+        <f>IFERROR(2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="E48" s="340">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H48" s="342">
+        <f>IFERROR(G48*E48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="343">
+        <f>IFERROR(100/100,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K48" s="342">
+        <f>IFERROR((I48-G48)*J48+G48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L48" s="342">
+        <f>IFERROR(K48*E48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="343">
+        <f>IFERROR(+Inputs!$L$7,0)</f>
+        <v>2.5E-2</v>
+      </c>
+      <c r="N48" s="343">
+        <f>IFERROR(+Inputs!$L$6,0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="O48" s="340">
+        <f>IFERROR(O10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P48" s="340">
+        <f>IFERROR(O48*E48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="342">
+        <f>IFERROR(K48/O48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R48" s="340">
+        <f>IFERROR(100,0)</f>
+        <v>100</v>
+      </c>
+      <c r="S48" s="340">
+        <f>IFERROR(R48*E48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T48" s="191"/>
+      <c r="U48" s="190"/>
+    </row>
+    <row r="49" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="189"/>
+      <c r="C49" s="354" t="inlineStr">
+        <is>
+          <t>Restricted Tier C 3BR</t>
+        </is>
+      </c>
+      <c r="D49" s="340">
+        <f>IFERROR(3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="E49" s="340">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="342">
+        <f>IFERROR(G49*E49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="342">
+        <f>IFERROR(0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="343">
+        <f>IFERROR(100/100,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K49" s="342">
+        <f>IFERROR((I49-G49)*J49+G49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="342">
+        <f>IFERROR(K49*E49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="343">
+        <f>IFERROR(+Inputs!$L$7,0)</f>
+        <v>2.5E-2</v>
+      </c>
+      <c r="N49" s="343">
+        <f>IFERROR(+Inputs!$L$6,0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="O49" s="340">
+        <f>IFERROR(O11,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P49" s="340">
+        <f>IFERROR(O49*E49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="342">
+        <f>IFERROR(K49/O49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R49" s="340">
+        <f>IFERROR(100,0)</f>
+        <v>100</v>
+      </c>
+      <c r="S49" s="340">
+        <f>IFERROR(R49*E49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T49" s="191"/>
+      <c r="U49" s="190"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C3:S3"/>
@@ -16635,7 +16961,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:DU104"/>
+  <dimension ref="A1:DU109"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.42578125" style="385" customWidth="1"/>
@@ -57689,7 +58015,7 @@
         <v>17170572.192158204</v>
       </c>
       <c r="F100" s="469">
-        <f t="shared" ref="F100:AK100" si="134">-F81+F56+F95+F96+F97+F98+F92</f>
+        <f t="shared" ref="F100:AK100" si="134">-F81+F56+F95+F96+F97+F98+F92+F106+F107+F108+F109</f>
         <v>-15820.442152306528</v>
       </c>
       <c r="G100" s="469">
@@ -57817,7 +58143,7 @@
         <v>0</v>
       </c>
       <c r="AL100" s="471">
-        <f t="shared" ref="AL100:BQ100" si="135">-AL81+AL56+AL95+AL96+AL97+AL98+AL92</f>
+        <f t="shared" ref="AL100:BQ100" si="135">-AL81+AL56+AL95+AL96+AL97+AL98+AL92+AL106+AL107+AL108+AL109</f>
         <v>18649884.010827802</v>
       </c>
       <c r="AM100" s="471">
@@ -57945,7 +58271,7 @@
         <v>158146.9684620531</v>
       </c>
       <c r="BR100" s="471">
-        <f t="shared" ref="BR100:CW100" si="136">-BR81+BR56+BR95+BR96+BR97+BR98+BR92</f>
+        <f t="shared" ref="BR100:CW100" si="136">-BR81+BR56+BR95+BR96+BR97+BR98+BR92+BR106+BR107+BR108+BR109</f>
         <v>158982.58283614716</v>
       </c>
       <c r="BS100" s="471">
@@ -58073,7 +58399,7 @@
         <v>0</v>
       </c>
       <c r="CX100" s="471">
-        <f t="shared" ref="CX100:DU100" si="137">-CX81+CX56+CX95+CX96+CX97+CX98+CX92</f>
+        <f t="shared" ref="CX100:DU100" si="137">-CX81+CX56+CX95+CX96+CX97+CX98+CX92+CX106+CX107+CX108+CX109</f>
         <v>0</v>
       </c>
       <c r="CY100" s="471">
@@ -58194,6 +58520,1954 @@
       <c r="F104" s="477">
         <f>SUMIF(F100:DM100,"&gt;0")/-SUMIF(F100:DM100,"&lt;0")</f>
         <v>1.720193531614989</v>
+      </c>
+    </row>
+    <row r="106" spans="1:125" x14ac:dyDescent="0.25">
+      <c r="D106" s="387" t="inlineStr">
+        <is>
+          <t>Sub Loan Proceeds</t>
+        </is>
+      </c>
+      <c r="F106" s="441">
+        <f>(F4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="G106" s="441">
+        <f>(G4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="H106" s="441">
+        <f>(H4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="I106" s="441">
+        <f>(I4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="J106" s="442">
+        <f>(J4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="K106" s="442">
+        <f>(K4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="L106" s="442">
+        <f>(L4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="M106" s="442">
+        <f>(M4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="N106" s="442">
+        <f>(N4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="O106" s="442">
+        <f>(O4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="P106" s="442">
+        <f>(P4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="Q106" s="442">
+        <f>(Q4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="R106" s="442">
+        <f>(R4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="S106" s="442">
+        <f>(S4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="T106" s="442">
+        <f>(T4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="U106" s="443">
+        <f>(U4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="V106" s="443">
+        <f>(V4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="W106" s="443">
+        <f>(W4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="X106" s="443">
+        <f>(X4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="Y106" s="443">
+        <f>(Y4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="Z106" s="443">
+        <f>(Z4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AA106" s="443">
+        <f>(AA4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AB106" s="443">
+        <f>(AB4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AC106" s="443">
+        <f>(AC4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AD106" s="443">
+        <f>(AD4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AE106" s="443">
+        <f>(AE4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AF106" s="443">
+        <f>(AF4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AG106" s="443">
+        <f>(AG4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AH106" s="443">
+        <f>(AH4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AI106" s="443">
+        <f>(AI4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ106" s="443">
+        <f>(AJ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AK106" s="443">
+        <f>(AK4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AL106" s="443">
+        <f>(AL4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AM106" s="443">
+        <f>(AM4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AN106" s="443">
+        <f>(AN4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AO106" s="443">
+        <f>(AO4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AP106" s="443">
+        <f>(AP4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ106" s="443">
+        <f>(AQ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AR106" s="443">
+        <f>(AR4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AS106" s="443">
+        <f>(AS4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AT106" s="443">
+        <f>(AT4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AU106" s="443">
+        <f>(AU4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AV106" s="443">
+        <f>(AV4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AW106" s="443">
+        <f>(AW4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AX106" s="443">
+        <f>(AX4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AY106" s="443">
+        <f>(AY4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ106" s="443">
+        <f>(AZ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BA106" s="443">
+        <f>(BA4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BB106" s="443">
+        <f>(BB4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BC106" s="443">
+        <f>(BC4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BD106" s="443">
+        <f>(BD4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BE106" s="443">
+        <f>(BE4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BF106" s="443">
+        <f>(BF4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BG106" s="443">
+        <f>(BG4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BH106" s="443">
+        <f>(BH4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BI106" s="443">
+        <f>(BI4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ106" s="443">
+        <f>(BJ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BK106" s="443">
+        <f>(BK4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BL106" s="443">
+        <f>(BL4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BM106" s="443">
+        <f>(BM4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BN106" s="443">
+        <f>(BN4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BO106" s="443">
+        <f>(BO4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BP106" s="443">
+        <f>(BP4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ106" s="443">
+        <f>(BQ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BR106" s="443">
+        <f>(BR4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BS106" s="443">
+        <f>(BS4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BT106" s="443">
+        <f>(BT4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BU106" s="443">
+        <f>(BU4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BV106" s="443">
+        <f>(BV4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BW106" s="443">
+        <f>(BW4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BX106" s="443">
+        <f>(BX4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BY106" s="443">
+        <f>(BY4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="BZ106" s="443">
+        <f>(BZ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CA106" s="443">
+        <f>(CA4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CB106" s="443">
+        <f>(CB4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CC106" s="443">
+        <f>(CC4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CD106" s="443">
+        <f>(CD4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CE106" s="443">
+        <f>(CE4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CF106" s="443">
+        <f>(CF4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CG106" s="443">
+        <f>(CG4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CH106" s="443">
+        <f>(CH4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CI106" s="443">
+        <f>(CI4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CJ106" s="443">
+        <f>(CJ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CK106" s="443">
+        <f>(CK4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CL106" s="443">
+        <f>(CL4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CM106" s="443">
+        <f>(CM4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CN106" s="443">
+        <f>(CN4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CO106" s="443">
+        <f>(CO4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CP106" s="443">
+        <f>(CP4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CQ106" s="443">
+        <f>(CQ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CR106" s="443">
+        <f>(CR4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CS106" s="443">
+        <f>(CS4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CT106" s="443">
+        <f>(CT4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CU106" s="443">
+        <f>(CU4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CV106" s="443">
+        <f>(CV4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CW106" s="443">
+        <f>(CW4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CX106" s="443">
+        <f>(CX4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CY106" s="443">
+        <f>(CY4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="CZ106" s="443">
+        <f>(CZ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DA106" s="443">
+        <f>(DA4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DB106" s="443">
+        <f>(DB4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DC106" s="443">
+        <f>(DC4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DD106" s="443">
+        <f>(DD4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DE106" s="443">
+        <f>(DE4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DF106" s="443">
+        <f>(DF4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DG106" s="443">
+        <f>(DG4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DH106" s="443">
+        <f>(DH4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DI106" s="443">
+        <f>(DI4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DJ106" s="443">
+        <f>(DJ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DK106" s="443">
+        <f>(DK4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DL106" s="443">
+        <f>(DL4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DM106" s="443">
+        <f>(DM4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DN106" s="443">
+        <f>(DN4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DO106" s="443">
+        <f>(DO4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DP106" s="443">
+        <f>(DP4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DQ106" s="443">
+        <f>(DQ4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DR106" s="443">
+        <f>(DR4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DS106" s="443">
+        <f>(DS4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DT106" s="443">
+        <f>(DT4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+      <c r="DU106" s="443">
+        <f>(DU4=refinance_date)*('(Z+) Financing'!$D$43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:125" x14ac:dyDescent="0.25">
+      <c r="D107" s="387" t="inlineStr">
+        <is>
+          <t>Sub Interest</t>
+        </is>
+      </c>
+      <c r="F107" s="441">
+        <f>IF(AND(F4&gt;refinance_date,F4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,F4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G107" s="441">
+        <f>IF(AND(G4&gt;refinance_date,G4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,G4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H107" s="441">
+        <f>IF(AND(H4&gt;refinance_date,H4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,H4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I107" s="441">
+        <f>IF(AND(I4&gt;refinance_date,I4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,I4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J107" s="442">
+        <f>IF(AND(J4&gt;refinance_date,J4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,J4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K107" s="442">
+        <f>IF(AND(K4&gt;refinance_date,K4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,K4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L107" s="442">
+        <f>IF(AND(L4&gt;refinance_date,L4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,L4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M107" s="442">
+        <f>IF(AND(M4&gt;refinance_date,M4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,M4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N107" s="442">
+        <f>IF(AND(N4&gt;refinance_date,N4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,N4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O107" s="442">
+        <f>IF(AND(O4&gt;refinance_date,O4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,O4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P107" s="442">
+        <f>IF(AND(P4&gt;refinance_date,P4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,P4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q107" s="442">
+        <f>IF(AND(Q4&gt;refinance_date,Q4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,Q4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R107" s="442">
+        <f>IF(AND(R4&gt;refinance_date,R4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,R4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S107" s="442">
+        <f>IF(AND(S4&gt;refinance_date,S4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,S4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T107" s="442">
+        <f>IF(AND(T4&gt;refinance_date,T4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,T4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U107" s="443">
+        <f>IF(AND(U4&gt;refinance_date,U4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,U4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V107" s="443">
+        <f>IF(AND(V4&gt;refinance_date,V4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,V4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="W107" s="443">
+        <f>IF(AND(W4&gt;refinance_date,W4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,W4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="X107" s="443">
+        <f>IF(AND(X4&gt;refinance_date,X4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,X4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y107" s="443">
+        <f>IF(AND(Y4&gt;refinance_date,Y4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,Y4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z107" s="443">
+        <f>IF(AND(Z4&gt;refinance_date,Z4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,Z4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA107" s="443">
+        <f>IF(AND(AA4&gt;refinance_date,AA4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AA4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB107" s="443">
+        <f>IF(AND(AB4&gt;refinance_date,AB4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AB4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC107" s="443">
+        <f>IF(AND(AC4&gt;refinance_date,AC4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AC4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD107" s="443">
+        <f>IF(AND(AD4&gt;refinance_date,AD4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AD4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE107" s="443">
+        <f>IF(AND(AE4&gt;refinance_date,AE4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AE4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF107" s="443">
+        <f>IF(AND(AF4&gt;refinance_date,AF4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AF4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG107" s="443">
+        <f>IF(AND(AG4&gt;refinance_date,AG4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AG4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH107" s="443">
+        <f>IF(AND(AH4&gt;refinance_date,AH4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AH4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI107" s="443">
+        <f>IF(AND(AI4&gt;refinance_date,AI4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AI4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ107" s="443">
+        <f>IF(AND(AJ4&gt;refinance_date,AJ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AJ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK107" s="443">
+        <f>IF(AND(AK4&gt;refinance_date,AK4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AK4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL107" s="443">
+        <f>IF(AND(AL4&gt;refinance_date,AL4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AL4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM107" s="443">
+        <f>IF(AND(AM4&gt;refinance_date,AM4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AM4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN107" s="443">
+        <f>IF(AND(AN4&gt;refinance_date,AN4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AN4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO107" s="443">
+        <f>IF(AND(AO4&gt;refinance_date,AO4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AO4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP107" s="443">
+        <f>IF(AND(AP4&gt;refinance_date,AP4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AP4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ107" s="443">
+        <f>IF(AND(AQ4&gt;refinance_date,AQ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AQ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR107" s="443">
+        <f>IF(AND(AR4&gt;refinance_date,AR4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AR4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS107" s="443">
+        <f>IF(AND(AS4&gt;refinance_date,AS4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AS4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT107" s="443">
+        <f>IF(AND(AT4&gt;refinance_date,AT4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AT4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU107" s="443">
+        <f>IF(AND(AU4&gt;refinance_date,AU4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AU4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV107" s="443">
+        <f>IF(AND(AV4&gt;refinance_date,AV4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AV4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW107" s="443">
+        <f>IF(AND(AW4&gt;refinance_date,AW4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AW4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX107" s="443">
+        <f>IF(AND(AX4&gt;refinance_date,AX4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AX4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY107" s="443">
+        <f>IF(AND(AY4&gt;refinance_date,AY4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AY4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ107" s="443">
+        <f>IF(AND(AZ4&gt;refinance_date,AZ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,AZ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA107" s="443">
+        <f>IF(AND(BA4&gt;refinance_date,BA4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BA4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB107" s="443">
+        <f>IF(AND(BB4&gt;refinance_date,BB4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BB4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC107" s="443">
+        <f>IF(AND(BC4&gt;refinance_date,BC4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BC4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD107" s="443">
+        <f>IF(AND(BD4&gt;refinance_date,BD4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BD4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE107" s="443">
+        <f>IF(AND(BE4&gt;refinance_date,BE4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BE4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF107" s="443">
+        <f>IF(AND(BF4&gt;refinance_date,BF4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BF4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG107" s="443">
+        <f>IF(AND(BG4&gt;refinance_date,BG4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BG4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH107" s="443">
+        <f>IF(AND(BH4&gt;refinance_date,BH4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BH4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI107" s="443">
+        <f>IF(AND(BI4&gt;refinance_date,BI4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BI4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ107" s="443">
+        <f>IF(AND(BJ4&gt;refinance_date,BJ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BJ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK107" s="443">
+        <f>IF(AND(BK4&gt;refinance_date,BK4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BK4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL107" s="443">
+        <f>IF(AND(BL4&gt;refinance_date,BL4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BL4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM107" s="443">
+        <f>IF(AND(BM4&gt;refinance_date,BM4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BM4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BN107" s="443">
+        <f>IF(AND(BN4&gt;refinance_date,BN4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BN4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BO107" s="443">
+        <f>IF(AND(BO4&gt;refinance_date,BO4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BO4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BP107" s="443">
+        <f>IF(AND(BP4&gt;refinance_date,BP4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BP4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ107" s="443">
+        <f>IF(AND(BQ4&gt;refinance_date,BQ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BQ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR107" s="443">
+        <f>IF(AND(BR4&gt;refinance_date,BR4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BR4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BS107" s="443">
+        <f>IF(AND(BS4&gt;refinance_date,BS4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BS4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BT107" s="443">
+        <f>IF(AND(BT4&gt;refinance_date,BT4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BT4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BU107" s="443">
+        <f>IF(AND(BU4&gt;refinance_date,BU4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BU4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BV107" s="443">
+        <f>IF(AND(BV4&gt;refinance_date,BV4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BV4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BW107" s="443">
+        <f>IF(AND(BW4&gt;refinance_date,BW4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BW4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BX107" s="443">
+        <f>IF(AND(BX4&gt;refinance_date,BX4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BX4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BY107" s="443">
+        <f>IF(AND(BY4&gt;refinance_date,BY4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BY4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BZ107" s="443">
+        <f>IF(AND(BZ4&gt;refinance_date,BZ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,BZ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CA107" s="443">
+        <f>IF(AND(CA4&gt;refinance_date,CA4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CA4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CB107" s="443">
+        <f>IF(AND(CB4&gt;refinance_date,CB4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CB4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CC107" s="443">
+        <f>IF(AND(CC4&gt;refinance_date,CC4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CC4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CD107" s="443">
+        <f>IF(AND(CD4&gt;refinance_date,CD4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CD4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CE107" s="443">
+        <f>IF(AND(CE4&gt;refinance_date,CE4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CE4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CF107" s="443">
+        <f>IF(AND(CF4&gt;refinance_date,CF4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CF4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CG107" s="443">
+        <f>IF(AND(CG4&gt;refinance_date,CG4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CG4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CH107" s="443">
+        <f>IF(AND(CH4&gt;refinance_date,CH4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CH4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CI107" s="443">
+        <f>IF(AND(CI4&gt;refinance_date,CI4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CI4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CJ107" s="443">
+        <f>IF(AND(CJ4&gt;refinance_date,CJ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CJ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CK107" s="443">
+        <f>IF(AND(CK4&gt;refinance_date,CK4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CK4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CL107" s="443">
+        <f>IF(AND(CL4&gt;refinance_date,CL4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CL4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CM107" s="443">
+        <f>IF(AND(CM4&gt;refinance_date,CM4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CM4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CN107" s="443">
+        <f>IF(AND(CN4&gt;refinance_date,CN4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CN4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CO107" s="443">
+        <f>IF(AND(CO4&gt;refinance_date,CO4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CO4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CP107" s="443">
+        <f>IF(AND(CP4&gt;refinance_date,CP4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CP4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CQ107" s="443">
+        <f>IF(AND(CQ4&gt;refinance_date,CQ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CQ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CR107" s="443">
+        <f>IF(AND(CR4&gt;refinance_date,CR4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CR4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CS107" s="443">
+        <f>IF(AND(CS4&gt;refinance_date,CS4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CS4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CT107" s="443">
+        <f>IF(AND(CT4&gt;refinance_date,CT4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CT4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CU107" s="443">
+        <f>IF(AND(CU4&gt;refinance_date,CU4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CU4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CV107" s="443">
+        <f>IF(AND(CV4&gt;refinance_date,CV4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CV4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CW107" s="443">
+        <f>IF(AND(CW4&gt;refinance_date,CW4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CW4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CX107" s="443">
+        <f>IF(AND(CX4&gt;refinance_date,CX4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CX4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CY107" s="443">
+        <f>IF(AND(CY4&gt;refinance_date,CY4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CY4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CZ107" s="443">
+        <f>IF(AND(CZ4&gt;refinance_date,CZ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,CZ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DA107" s="443">
+        <f>IF(AND(DA4&gt;refinance_date,DA4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DA4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DB107" s="443">
+        <f>IF(AND(DB4&gt;refinance_date,DB4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DB4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DC107" s="443">
+        <f>IF(AND(DC4&gt;refinance_date,DC4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DC4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DD107" s="443">
+        <f>IF(AND(DD4&gt;refinance_date,DD4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DD4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE107" s="443">
+        <f>IF(AND(DE4&gt;refinance_date,DE4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DE4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DF107" s="443">
+        <f>IF(AND(DF4&gt;refinance_date,DF4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DF4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DG107" s="443">
+        <f>IF(AND(DG4&gt;refinance_date,DG4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DG4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DH107" s="443">
+        <f>IF(AND(DH4&gt;refinance_date,DH4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DH4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DI107" s="443">
+        <f>IF(AND(DI4&gt;refinance_date,DI4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DI4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DJ107" s="443">
+        <f>IF(AND(DJ4&gt;refinance_date,DJ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DJ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DK107" s="443">
+        <f>IF(AND(DK4&gt;refinance_date,DK4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DK4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL107" s="443">
+        <f>IF(AND(DL4&gt;refinance_date,DL4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DL4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DM107" s="443">
+        <f>IF(AND(DM4&gt;refinance_date,DM4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DM4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DN107" s="443">
+        <f>IF(AND(DN4&gt;refinance_date,DN4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DN4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DO107" s="443">
+        <f>IF(AND(DO4&gt;refinance_date,DO4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DO4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DP107" s="443">
+        <f>IF(AND(DP4&gt;refinance_date,DP4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DP4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DQ107" s="443">
+        <f>IF(AND(DQ4&gt;refinance_date,DQ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DQ4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DR107" s="443">
+        <f>IF(AND(DR4&gt;refinance_date,DR4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DR4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS107" s="443">
+        <f>IF(AND(DS4&gt;refinance_date,DS4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DS4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DT107" s="443">
+        <f>IF(AND(DT4&gt;refinance_date,DT4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DT4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DU107" s="443">
+        <f>IF(AND(DU4&gt;refinance_date,DU4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,IPMT('(Z+) Financing'!$D$44*365.25/360/12,ROUND(DAYS360(refinance_date,DU4)/30,0),'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43),-'(Z+) Financing'!$D$43*'(Z+) Financing'!$D$44*365.25/360/12),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:125" x14ac:dyDescent="0.25">
+      <c r="D108" s="387" t="inlineStr">
+        <is>
+          <t>Sub Principal</t>
+        </is>
+      </c>
+      <c r="F108" s="441">
+        <f>IF(AND(F4&gt;refinance_date,F4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-F107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G108" s="441">
+        <f>IF(AND(G4&gt;refinance_date,G4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-G107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H108" s="441">
+        <f>IF(AND(H4&gt;refinance_date,H4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-H107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I108" s="441">
+        <f>IF(AND(I4&gt;refinance_date,I4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-I107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J108" s="442">
+        <f>IF(AND(J4&gt;refinance_date,J4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-J107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K108" s="442">
+        <f>IF(AND(K4&gt;refinance_date,K4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-K107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L108" s="442">
+        <f>IF(AND(L4&gt;refinance_date,L4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-L107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M108" s="442">
+        <f>IF(AND(M4&gt;refinance_date,M4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-M107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N108" s="442">
+        <f>IF(AND(N4&gt;refinance_date,N4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-N107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O108" s="442">
+        <f>IF(AND(O4&gt;refinance_date,O4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-O107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P108" s="442">
+        <f>IF(AND(P4&gt;refinance_date,P4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-P107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q108" s="442">
+        <f>IF(AND(Q4&gt;refinance_date,Q4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-Q107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R108" s="442">
+        <f>IF(AND(R4&gt;refinance_date,R4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-R107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S108" s="442">
+        <f>IF(AND(S4&gt;refinance_date,S4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-S107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T108" s="442">
+        <f>IF(AND(T4&gt;refinance_date,T4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-T107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U108" s="443">
+        <f>IF(AND(U4&gt;refinance_date,U4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-U107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V108" s="443">
+        <f>IF(AND(V4&gt;refinance_date,V4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-V107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="W108" s="443">
+        <f>IF(AND(W4&gt;refinance_date,W4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-W107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="X108" s="443">
+        <f>IF(AND(X4&gt;refinance_date,X4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-X107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y108" s="443">
+        <f>IF(AND(Y4&gt;refinance_date,Y4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-Y107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z108" s="443">
+        <f>IF(AND(Z4&gt;refinance_date,Z4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-Z107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA108" s="443">
+        <f>IF(AND(AA4&gt;refinance_date,AA4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AA107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB108" s="443">
+        <f>IF(AND(AB4&gt;refinance_date,AB4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AB107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC108" s="443">
+        <f>IF(AND(AC4&gt;refinance_date,AC4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AC107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD108" s="443">
+        <f>IF(AND(AD4&gt;refinance_date,AD4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AD107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE108" s="443">
+        <f>IF(AND(AE4&gt;refinance_date,AE4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AE107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF108" s="443">
+        <f>IF(AND(AF4&gt;refinance_date,AF4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AF107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG108" s="443">
+        <f>IF(AND(AG4&gt;refinance_date,AG4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AG107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH108" s="443">
+        <f>IF(AND(AH4&gt;refinance_date,AH4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AH107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI108" s="443">
+        <f>IF(AND(AI4&gt;refinance_date,AI4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AI107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ108" s="443">
+        <f>IF(AND(AJ4&gt;refinance_date,AJ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AJ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK108" s="443">
+        <f>IF(AND(AK4&gt;refinance_date,AK4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AK107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL108" s="443">
+        <f>IF(AND(AL4&gt;refinance_date,AL4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AL107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM108" s="443">
+        <f>IF(AND(AM4&gt;refinance_date,AM4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AM107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN108" s="443">
+        <f>IF(AND(AN4&gt;refinance_date,AN4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AN107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO108" s="443">
+        <f>IF(AND(AO4&gt;refinance_date,AO4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AO107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP108" s="443">
+        <f>IF(AND(AP4&gt;refinance_date,AP4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AP107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ108" s="443">
+        <f>IF(AND(AQ4&gt;refinance_date,AQ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AQ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR108" s="443">
+        <f>IF(AND(AR4&gt;refinance_date,AR4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AR107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS108" s="443">
+        <f>IF(AND(AS4&gt;refinance_date,AS4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AS107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT108" s="443">
+        <f>IF(AND(AT4&gt;refinance_date,AT4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AT107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU108" s="443">
+        <f>IF(AND(AU4&gt;refinance_date,AU4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AU107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV108" s="443">
+        <f>IF(AND(AV4&gt;refinance_date,AV4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AV107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW108" s="443">
+        <f>IF(AND(AW4&gt;refinance_date,AW4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AW107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX108" s="443">
+        <f>IF(AND(AX4&gt;refinance_date,AX4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AX107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY108" s="443">
+        <f>IF(AND(AY4&gt;refinance_date,AY4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AY107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ108" s="443">
+        <f>IF(AND(AZ4&gt;refinance_date,AZ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-AZ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA108" s="443">
+        <f>IF(AND(BA4&gt;refinance_date,BA4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BA107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB108" s="443">
+        <f>IF(AND(BB4&gt;refinance_date,BB4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BB107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC108" s="443">
+        <f>IF(AND(BC4&gt;refinance_date,BC4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BC107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD108" s="443">
+        <f>IF(AND(BD4&gt;refinance_date,BD4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BD107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE108" s="443">
+        <f>IF(AND(BE4&gt;refinance_date,BE4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BE107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF108" s="443">
+        <f>IF(AND(BF4&gt;refinance_date,BF4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BF107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG108" s="443">
+        <f>IF(AND(BG4&gt;refinance_date,BG4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BG107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH108" s="443">
+        <f>IF(AND(BH4&gt;refinance_date,BH4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BH107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI108" s="443">
+        <f>IF(AND(BI4&gt;refinance_date,BI4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BI107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ108" s="443">
+        <f>IF(AND(BJ4&gt;refinance_date,BJ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BJ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK108" s="443">
+        <f>IF(AND(BK4&gt;refinance_date,BK4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BK107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL108" s="443">
+        <f>IF(AND(BL4&gt;refinance_date,BL4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BL107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM108" s="443">
+        <f>IF(AND(BM4&gt;refinance_date,BM4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BM107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BN108" s="443">
+        <f>IF(AND(BN4&gt;refinance_date,BN4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BN107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BO108" s="443">
+        <f>IF(AND(BO4&gt;refinance_date,BO4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BO107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BP108" s="443">
+        <f>IF(AND(BP4&gt;refinance_date,BP4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BP107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ108" s="443">
+        <f>IF(AND(BQ4&gt;refinance_date,BQ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BQ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR108" s="443">
+        <f>IF(AND(BR4&gt;refinance_date,BR4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BR107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BS108" s="443">
+        <f>IF(AND(BS4&gt;refinance_date,BS4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BS107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BT108" s="443">
+        <f>IF(AND(BT4&gt;refinance_date,BT4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BT107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BU108" s="443">
+        <f>IF(AND(BU4&gt;refinance_date,BU4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BU107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BV108" s="443">
+        <f>IF(AND(BV4&gt;refinance_date,BV4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BV107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BW108" s="443">
+        <f>IF(AND(BW4&gt;refinance_date,BW4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BW107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BX108" s="443">
+        <f>IF(AND(BX4&gt;refinance_date,BX4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BX107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BY108" s="443">
+        <f>IF(AND(BY4&gt;refinance_date,BY4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BY107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BZ108" s="443">
+        <f>IF(AND(BZ4&gt;refinance_date,BZ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-BZ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CA108" s="443">
+        <f>IF(AND(CA4&gt;refinance_date,CA4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CA107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CB108" s="443">
+        <f>IF(AND(CB4&gt;refinance_date,CB4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CB107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CC108" s="443">
+        <f>IF(AND(CC4&gt;refinance_date,CC4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CC107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CD108" s="443">
+        <f>IF(AND(CD4&gt;refinance_date,CD4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CD107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CE108" s="443">
+        <f>IF(AND(CE4&gt;refinance_date,CE4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CE107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CF108" s="443">
+        <f>IF(AND(CF4&gt;refinance_date,CF4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CF107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CG108" s="443">
+        <f>IF(AND(CG4&gt;refinance_date,CG4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CG107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CH108" s="443">
+        <f>IF(AND(CH4&gt;refinance_date,CH4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CH107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CI108" s="443">
+        <f>IF(AND(CI4&gt;refinance_date,CI4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CI107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CJ108" s="443">
+        <f>IF(AND(CJ4&gt;refinance_date,CJ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CJ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CK108" s="443">
+        <f>IF(AND(CK4&gt;refinance_date,CK4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CK107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CL108" s="443">
+        <f>IF(AND(CL4&gt;refinance_date,CL4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CL107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CM108" s="443">
+        <f>IF(AND(CM4&gt;refinance_date,CM4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CM107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CN108" s="443">
+        <f>IF(AND(CN4&gt;refinance_date,CN4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CN107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CO108" s="443">
+        <f>IF(AND(CO4&gt;refinance_date,CO4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CO107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CP108" s="443">
+        <f>IF(AND(CP4&gt;refinance_date,CP4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CP107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CQ108" s="443">
+        <f>IF(AND(CQ4&gt;refinance_date,CQ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CQ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CR108" s="443">
+        <f>IF(AND(CR4&gt;refinance_date,CR4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CR107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CS108" s="443">
+        <f>IF(AND(CS4&gt;refinance_date,CS4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CS107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CT108" s="443">
+        <f>IF(AND(CT4&gt;refinance_date,CT4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CT107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CU108" s="443">
+        <f>IF(AND(CU4&gt;refinance_date,CU4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CU107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CV108" s="443">
+        <f>IF(AND(CV4&gt;refinance_date,CV4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CV107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CW108" s="443">
+        <f>IF(AND(CW4&gt;refinance_date,CW4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CW107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CX108" s="443">
+        <f>IF(AND(CX4&gt;refinance_date,CX4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CX107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CY108" s="443">
+        <f>IF(AND(CY4&gt;refinance_date,CY4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CY107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="CZ108" s="443">
+        <f>IF(AND(CZ4&gt;refinance_date,CZ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-CZ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DA108" s="443">
+        <f>IF(AND(DA4&gt;refinance_date,DA4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DA107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DB108" s="443">
+        <f>IF(AND(DB4&gt;refinance_date,DB4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DB107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DC108" s="443">
+        <f>IF(AND(DC4&gt;refinance_date,DC4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DC107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DD108" s="443">
+        <f>IF(AND(DD4&gt;refinance_date,DD4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DD107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE108" s="443">
+        <f>IF(AND(DE4&gt;refinance_date,DE4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DE107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DF108" s="443">
+        <f>IF(AND(DF4&gt;refinance_date,DF4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DF107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DG108" s="443">
+        <f>IF(AND(DG4&gt;refinance_date,DG4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DG107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DH108" s="443">
+        <f>IF(AND(DH4&gt;refinance_date,DH4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DH107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DI108" s="443">
+        <f>IF(AND(DI4&gt;refinance_date,DI4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DI107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DJ108" s="443">
+        <f>IF(AND(DJ4&gt;refinance_date,DJ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DJ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DK108" s="443">
+        <f>IF(AND(DK4&gt;refinance_date,DK4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DK107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL108" s="443">
+        <f>IF(AND(DL4&gt;refinance_date,DL4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DL107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DM108" s="443">
+        <f>IF(AND(DM4&gt;refinance_date,DM4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DM107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DN108" s="443">
+        <f>IF(AND(DN4&gt;refinance_date,DN4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DN107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DO108" s="443">
+        <f>IF(AND(DO4&gt;refinance_date,DO4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DO107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DP108" s="443">
+        <f>IF(AND(DP4&gt;refinance_date,DP4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DP107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DQ108" s="443">
+        <f>IF(AND(DQ4&gt;refinance_date,DQ4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DQ107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DR108" s="443">
+        <f>IF(AND(DR4&gt;refinance_date,DR4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DR107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS108" s="443">
+        <f>IF(AND(DS4&gt;refinance_date,DS4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DS107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DT108" s="443">
+        <f>IF(AND(DT4&gt;refinance_date,DT4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DT107,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DU108" s="443">
+        <f>IF(AND(DU4&gt;refinance_date,DU4&lt;=sale_month),IF('(Z+) Financing'!$D$45&gt;0,PMT('(Z+) Financing'!$D$44*365.25/360/12,'(Z+) Financing'!$D$45*12,'(Z+) Financing'!$D$43)-DU107,0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:125" x14ac:dyDescent="0.25">
+      <c r="D109" s="387" t="inlineStr">
+        <is>
+          <t>Sub Payoff</t>
+        </is>
+      </c>
+      <c r="F109" s="441">
+        <f>(F4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:F108))</f>
+        <v>0</v>
+      </c>
+      <c r="G109" s="441">
+        <f>(G4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:G108))</f>
+        <v>0</v>
+      </c>
+      <c r="H109" s="441">
+        <f>(H4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:H108))</f>
+        <v>0</v>
+      </c>
+      <c r="I109" s="441">
+        <f>(I4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:I108))</f>
+        <v>0</v>
+      </c>
+      <c r="J109" s="442">
+        <f>(J4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:J108))</f>
+        <v>0</v>
+      </c>
+      <c r="K109" s="442">
+        <f>(K4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:K108))</f>
+        <v>0</v>
+      </c>
+      <c r="L109" s="442">
+        <f>(L4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:L108))</f>
+        <v>0</v>
+      </c>
+      <c r="M109" s="442">
+        <f>(M4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:M108))</f>
+        <v>0</v>
+      </c>
+      <c r="N109" s="442">
+        <f>(N4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:N108))</f>
+        <v>0</v>
+      </c>
+      <c r="O109" s="442">
+        <f>(O4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:O108))</f>
+        <v>0</v>
+      </c>
+      <c r="P109" s="442">
+        <f>(P4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:P108))</f>
+        <v>0</v>
+      </c>
+      <c r="Q109" s="442">
+        <f>(Q4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:Q108))</f>
+        <v>0</v>
+      </c>
+      <c r="R109" s="442">
+        <f>(R4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:R108))</f>
+        <v>0</v>
+      </c>
+      <c r="S109" s="442">
+        <f>(S4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:S108))</f>
+        <v>0</v>
+      </c>
+      <c r="T109" s="442">
+        <f>(T4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:T108))</f>
+        <v>0</v>
+      </c>
+      <c r="U109" s="443">
+        <f>(U4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:U108))</f>
+        <v>0</v>
+      </c>
+      <c r="V109" s="443">
+        <f>(V4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:V108))</f>
+        <v>0</v>
+      </c>
+      <c r="W109" s="443">
+        <f>(W4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:W108))</f>
+        <v>0</v>
+      </c>
+      <c r="X109" s="443">
+        <f>(X4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:X108))</f>
+        <v>0</v>
+      </c>
+      <c r="Y109" s="443">
+        <f>(Y4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:Y108))</f>
+        <v>0</v>
+      </c>
+      <c r="Z109" s="443">
+        <f>(Z4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:Z108))</f>
+        <v>0</v>
+      </c>
+      <c r="AA109" s="443">
+        <f>(AA4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AA108))</f>
+        <v>0</v>
+      </c>
+      <c r="AB109" s="443">
+        <f>(AB4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AB108))</f>
+        <v>0</v>
+      </c>
+      <c r="AC109" s="443">
+        <f>(AC4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AC108))</f>
+        <v>0</v>
+      </c>
+      <c r="AD109" s="443">
+        <f>(AD4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AD108))</f>
+        <v>0</v>
+      </c>
+      <c r="AE109" s="443">
+        <f>(AE4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AE108))</f>
+        <v>0</v>
+      </c>
+      <c r="AF109" s="443">
+        <f>(AF4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AF108))</f>
+        <v>0</v>
+      </c>
+      <c r="AG109" s="443">
+        <f>(AG4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AG108))</f>
+        <v>0</v>
+      </c>
+      <c r="AH109" s="443">
+        <f>(AH4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AH108))</f>
+        <v>0</v>
+      </c>
+      <c r="AI109" s="443">
+        <f>(AI4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AI108))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="443">
+        <f>(AJ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AJ108))</f>
+        <v>0</v>
+      </c>
+      <c r="AK109" s="443">
+        <f>(AK4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AK108))</f>
+        <v>0</v>
+      </c>
+      <c r="AL109" s="443">
+        <f>(AL4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AL108))</f>
+        <v>0</v>
+      </c>
+      <c r="AM109" s="443">
+        <f>(AM4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AM108))</f>
+        <v>0</v>
+      </c>
+      <c r="AN109" s="443">
+        <f>(AN4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AN108))</f>
+        <v>0</v>
+      </c>
+      <c r="AO109" s="443">
+        <f>(AO4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AO108))</f>
+        <v>0</v>
+      </c>
+      <c r="AP109" s="443">
+        <f>(AP4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AP108))</f>
+        <v>0</v>
+      </c>
+      <c r="AQ109" s="443">
+        <f>(AQ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AQ108))</f>
+        <v>0</v>
+      </c>
+      <c r="AR109" s="443">
+        <f>(AR4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AR108))</f>
+        <v>0</v>
+      </c>
+      <c r="AS109" s="443">
+        <f>(AS4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AS108))</f>
+        <v>0</v>
+      </c>
+      <c r="AT109" s="443">
+        <f>(AT4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AT108))</f>
+        <v>0</v>
+      </c>
+      <c r="AU109" s="443">
+        <f>(AU4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AU108))</f>
+        <v>0</v>
+      </c>
+      <c r="AV109" s="443">
+        <f>(AV4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AV108))</f>
+        <v>0</v>
+      </c>
+      <c r="AW109" s="443">
+        <f>(AW4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AW108))</f>
+        <v>0</v>
+      </c>
+      <c r="AX109" s="443">
+        <f>(AX4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AX108))</f>
+        <v>0</v>
+      </c>
+      <c r="AY109" s="443">
+        <f>(AY4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AY108))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ109" s="443">
+        <f>(AZ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:AZ108))</f>
+        <v>0</v>
+      </c>
+      <c r="BA109" s="443">
+        <f>(BA4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BA108))</f>
+        <v>0</v>
+      </c>
+      <c r="BB109" s="443">
+        <f>(BB4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BB108))</f>
+        <v>0</v>
+      </c>
+      <c r="BC109" s="443">
+        <f>(BC4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BC108))</f>
+        <v>0</v>
+      </c>
+      <c r="BD109" s="443">
+        <f>(BD4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BD108))</f>
+        <v>0</v>
+      </c>
+      <c r="BE109" s="443">
+        <f>(BE4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BE108))</f>
+        <v>0</v>
+      </c>
+      <c r="BF109" s="443">
+        <f>(BF4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BF108))</f>
+        <v>0</v>
+      </c>
+      <c r="BG109" s="443">
+        <f>(BG4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BG108))</f>
+        <v>0</v>
+      </c>
+      <c r="BH109" s="443">
+        <f>(BH4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BH108))</f>
+        <v>0</v>
+      </c>
+      <c r="BI109" s="443">
+        <f>(BI4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BI108))</f>
+        <v>0</v>
+      </c>
+      <c r="BJ109" s="443">
+        <f>(BJ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BJ108))</f>
+        <v>0</v>
+      </c>
+      <c r="BK109" s="443">
+        <f>(BK4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BK108))</f>
+        <v>0</v>
+      </c>
+      <c r="BL109" s="443">
+        <f>(BL4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BL108))</f>
+        <v>0</v>
+      </c>
+      <c r="BM109" s="443">
+        <f>(BM4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BM108))</f>
+        <v>0</v>
+      </c>
+      <c r="BN109" s="443">
+        <f>(BN4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BN108))</f>
+        <v>0</v>
+      </c>
+      <c r="BO109" s="443">
+        <f>(BO4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BO108))</f>
+        <v>0</v>
+      </c>
+      <c r="BP109" s="443">
+        <f>(BP4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BP108))</f>
+        <v>0</v>
+      </c>
+      <c r="BQ109" s="443">
+        <f>(BQ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BQ108))</f>
+        <v>0</v>
+      </c>
+      <c r="BR109" s="443">
+        <f>(BR4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BR108))</f>
+        <v>0</v>
+      </c>
+      <c r="BS109" s="443">
+        <f>(BS4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BS108))</f>
+        <v>0</v>
+      </c>
+      <c r="BT109" s="443">
+        <f>(BT4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BT108))</f>
+        <v>0</v>
+      </c>
+      <c r="BU109" s="443">
+        <f>(BU4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BU108))</f>
+        <v>0</v>
+      </c>
+      <c r="BV109" s="443">
+        <f>(BV4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BV108))</f>
+        <v>0</v>
+      </c>
+      <c r="BW109" s="443">
+        <f>(BW4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BW108))</f>
+        <v>0</v>
+      </c>
+      <c r="BX109" s="443">
+        <f>(BX4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BX108))</f>
+        <v>0</v>
+      </c>
+      <c r="BY109" s="443">
+        <f>(BY4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BY108))</f>
+        <v>0</v>
+      </c>
+      <c r="BZ109" s="443">
+        <f>(BZ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:BZ108))</f>
+        <v>0</v>
+      </c>
+      <c r="CA109" s="443">
+        <f>(CA4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CA108))</f>
+        <v>0</v>
+      </c>
+      <c r="CB109" s="443">
+        <f>(CB4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CB108))</f>
+        <v>0</v>
+      </c>
+      <c r="CC109" s="443">
+        <f>(CC4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CC108))</f>
+        <v>0</v>
+      </c>
+      <c r="CD109" s="443">
+        <f>(CD4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CD108))</f>
+        <v>0</v>
+      </c>
+      <c r="CE109" s="443">
+        <f>(CE4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CE108))</f>
+        <v>0</v>
+      </c>
+      <c r="CF109" s="443">
+        <f>(CF4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CF108))</f>
+        <v>0</v>
+      </c>
+      <c r="CG109" s="443">
+        <f>(CG4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CG108))</f>
+        <v>0</v>
+      </c>
+      <c r="CH109" s="443">
+        <f>(CH4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CH108))</f>
+        <v>0</v>
+      </c>
+      <c r="CI109" s="443">
+        <f>(CI4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CI108))</f>
+        <v>0</v>
+      </c>
+      <c r="CJ109" s="443">
+        <f>(CJ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CJ108))</f>
+        <v>0</v>
+      </c>
+      <c r="CK109" s="443">
+        <f>(CK4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CK108))</f>
+        <v>0</v>
+      </c>
+      <c r="CL109" s="443">
+        <f>(CL4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CL108))</f>
+        <v>0</v>
+      </c>
+      <c r="CM109" s="443">
+        <f>(CM4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CM108))</f>
+        <v>0</v>
+      </c>
+      <c r="CN109" s="443">
+        <f>(CN4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CN108))</f>
+        <v>0</v>
+      </c>
+      <c r="CO109" s="443">
+        <f>(CO4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CO108))</f>
+        <v>0</v>
+      </c>
+      <c r="CP109" s="443">
+        <f>(CP4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CP108))</f>
+        <v>0</v>
+      </c>
+      <c r="CQ109" s="443">
+        <f>(CQ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CQ108))</f>
+        <v>0</v>
+      </c>
+      <c r="CR109" s="443">
+        <f>(CR4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CR108))</f>
+        <v>0</v>
+      </c>
+      <c r="CS109" s="443">
+        <f>(CS4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CS108))</f>
+        <v>0</v>
+      </c>
+      <c r="CT109" s="443">
+        <f>(CT4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CT108))</f>
+        <v>0</v>
+      </c>
+      <c r="CU109" s="443">
+        <f>(CU4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CU108))</f>
+        <v>0</v>
+      </c>
+      <c r="CV109" s="443">
+        <f>(CV4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CV108))</f>
+        <v>0</v>
+      </c>
+      <c r="CW109" s="443">
+        <f>(CW4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CW108))</f>
+        <v>0</v>
+      </c>
+      <c r="CX109" s="443">
+        <f>(CX4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CX108))</f>
+        <v>0</v>
+      </c>
+      <c r="CY109" s="443">
+        <f>(CY4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CY108))</f>
+        <v>0</v>
+      </c>
+      <c r="CZ109" s="443">
+        <f>(CZ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:CZ108))</f>
+        <v>0</v>
+      </c>
+      <c r="DA109" s="443">
+        <f>(DA4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DA108))</f>
+        <v>0</v>
+      </c>
+      <c r="DB109" s="443">
+        <f>(DB4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DB108))</f>
+        <v>0</v>
+      </c>
+      <c r="DC109" s="443">
+        <f>(DC4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DC108))</f>
+        <v>0</v>
+      </c>
+      <c r="DD109" s="443">
+        <f>(DD4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DD108))</f>
+        <v>0</v>
+      </c>
+      <c r="DE109" s="443">
+        <f>(DE4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DE108))</f>
+        <v>0</v>
+      </c>
+      <c r="DF109" s="443">
+        <f>(DF4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DF108))</f>
+        <v>0</v>
+      </c>
+      <c r="DG109" s="443">
+        <f>(DG4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DG108))</f>
+        <v>0</v>
+      </c>
+      <c r="DH109" s="443">
+        <f>(DH4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DH108))</f>
+        <v>0</v>
+      </c>
+      <c r="DI109" s="443">
+        <f>(DI4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DI108))</f>
+        <v>0</v>
+      </c>
+      <c r="DJ109" s="443">
+        <f>(DJ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DJ108))</f>
+        <v>0</v>
+      </c>
+      <c r="DK109" s="443">
+        <f>(DK4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DK108))</f>
+        <v>0</v>
+      </c>
+      <c r="DL109" s="443">
+        <f>(DL4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DL108))</f>
+        <v>0</v>
+      </c>
+      <c r="DM109" s="443">
+        <f>(DM4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DM108))</f>
+        <v>0</v>
+      </c>
+      <c r="DN109" s="443">
+        <f>(DN4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DN108))</f>
+        <v>0</v>
+      </c>
+      <c r="DO109" s="443">
+        <f>(DO4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DO108))</f>
+        <v>0</v>
+      </c>
+      <c r="DP109" s="443">
+        <f>(DP4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DP108))</f>
+        <v>0</v>
+      </c>
+      <c r="DQ109" s="443">
+        <f>(DQ4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DQ108))</f>
+        <v>0</v>
+      </c>
+      <c r="DR109" s="443">
+        <f>(DR4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DR108))</f>
+        <v>0</v>
+      </c>
+      <c r="DS109" s="443">
+        <f>(DS4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DS108))</f>
+        <v>0</v>
+      </c>
+      <c r="DT109" s="443">
+        <f>(DT4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DT108))</f>
+        <v>0</v>
+      </c>
+      <c r="DU109" s="443">
+        <f>(DU4=sale_month)*(-'(Z+) Financing'!$D$43-SUM($F$108:DU108))</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
